--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-10-07T18:06:14.412Z</t>
+    <t>2026-10-07T19:19:04.873Z</t>
   </si>
   <si>
     <t>Maurice Blackburn | Personal Injury &amp; Compensation Lawyers</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-10-07T19:19:04.873Z</t>
+    <t>2026-10-07T19:42:53.079Z</t>
   </si>
   <si>
     <t>Maurice Blackburn | Personal Injury &amp; Compensation Lawyers</t>
